--- a/output/log/fourthVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/log/fourthVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1165,9 +1165,9 @@
     <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】容積率（P002-00 修正百分比）
-填寫值：-6.25
+填寫值：6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = -6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1426,7 +1426,7 @@
     <comment ref="E11" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(1)土地使用管制 百分比小計（P002-00）
-填寫值：-6.25
+填寫值：6.25
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group1</t>
@@ -1489,9 +1489,9 @@
     <comment ref="G12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
-填寫值：-15.0
+填寫值：15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = -15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1516,9 +1516,9 @@
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
-填寫值：-11.25
+填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1543,9 +1543,9 @@
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
-填寫值：-11.25
+填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1588,9 +1588,9 @@
     <comment ref="G13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
-填寫值：-6.0
+填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1615,9 +1615,9 @@
     <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
-填寫值：-6.0
+填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1642,9 +1642,9 @@
     <comment ref="M13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
-填寫值：-6.0
+填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1687,9 +1687,9 @@
     <comment ref="G14" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近大型車站之程度（P002-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.near_station</t>
       </text>
     </comment>
@@ -1840,9 +1840,9 @@
     <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】站牌之接近程度或密集程度（P004-00 修正百分比）
-填寫值：-1.0
+填寫值：1.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = -1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_busstop</t>
       </text>
     </comment>
@@ -1939,9 +1939,9 @@
     <comment ref="M16" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】交流道之有無及接近交流道之程度（P004-00 修正百分比）
-填寫值：-1.0
+填寫值：1.0
 資料來源：比準地 P001-00 稍劣(4) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = -1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_interchange</t>
       </text>
     </comment>
@@ -1984,9 +1984,9 @@
     <comment ref="G17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
-填寫值：-2.5
+填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2011,9 +2011,9 @@
     <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2038,16 +2038,16 @@
     <comment ref="M17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P002-00）
-填寫值：-21.0
+填寫值：21.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2056,7 +2056,7 @@
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P003-00）
-填寫值：-14.75
+填寫值：14.75
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2065,7 +2065,7 @@
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P004-00）
-填寫值：-16.75
+填寫值：16.75
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2857,9 +2857,9 @@
     <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P002-00 修正百分比）
-填寫值：4.0
+填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2884,9 +2884,9 @@
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P003-00 修正百分比）
-填寫值：4.0
+填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2911,9 +2911,9 @@
     <comment ref="M28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P004-00 修正百分比）
-填寫值：2.0
+填寫值：-2.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = +2.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3010,9 +3010,9 @@
     <comment ref="M29" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近公園（里鄰公園、一般公園）、廣場、徒步區之程度（P004-00 修正百分比）
-填寫值：-4.0
+填寫值：4.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 普通(3)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00
 基準表項目ID：shulin.regional.near_park</t>
       </text>
     </comment>
@@ -3055,9 +3055,9 @@
     <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P002-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3082,9 +3082,9 @@
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P003-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3109,9 +3109,9 @@
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P004-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3154,9 +3154,9 @@
     <comment ref="G31" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】停車場地之便利程度（P002-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3181,9 +3181,9 @@
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】停車場地之便利程度（P003-00 修正百分比）
-填寫值：-1.5
+填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3316,7 +3316,7 @@
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P002-00）
-填寫值：1.0
+填寫值：-1.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3325,7 +3325,7 @@
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P003-00）
-填寫值：1.0
+填寫值：-1.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3334,7 +3334,7 @@
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P004-00）
-填寫值：-3.5
+填寫值：3.5
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="G8" s="68" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="H8" s="72" t="n">
         <v>3</v>
@@ -5223,7 +5223,7 @@
       <c r="C11" s="65" t="n"/>
       <c r="D11" s="60" t="n"/>
       <c r="E11" s="78" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="F11" s="63" t="n"/>
       <c r="G11" s="36" t="inlineStr">
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="G12" s="75" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="H12" s="74" t="n">
         <v>4</v>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="J12" s="75" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="K12" s="74" t="n">
         <v>4</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="M12" s="75" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="N12" s="13" t="n"/>
       <c r="O12" s="6" t="n"/>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="G13" s="75" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="H13" s="74" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="J13" s="75" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="K13" s="74" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="M13" s="75" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="N13" s="13" t="n"/>
       <c r="O13" s="6" t="n"/>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G14" s="75" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H14" s="74" t="n">
         <v>2</v>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="M15" s="75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N15" s="13" t="n"/>
       <c r="O15" s="6" t="n"/>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="M16" s="75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N16" s="13" t="n"/>
       <c r="O16" s="6" t="n"/>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="G17" s="75" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="H17" s="74" t="n">
         <v>1</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="J17" s="75" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K17" s="74" t="n">
         <v>1</v>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="M17" s="75" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="N17" s="13" t="n"/>
       <c r="O17" s="6" t="n"/>
@@ -5586,7 +5586,7 @@
       <c r="C18" s="65" t="n"/>
       <c r="D18" s="60" t="n"/>
       <c r="E18" s="78" t="n">
-        <v>-21</v>
+        <v>21</v>
       </c>
       <c r="F18" s="63" t="n"/>
       <c r="G18" s="36" t="inlineStr">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="H18" s="78" t="n">
-        <v>-14.75</v>
+        <v>14.75</v>
       </c>
       <c r="I18" s="63" t="n"/>
       <c r="J18" s="36" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="K18" s="78" t="n">
-        <v>-16.75</v>
+        <v>16.75</v>
       </c>
       <c r="L18" s="63" t="n"/>
       <c r="M18" s="36" t="inlineStr">
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="G28" s="75" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="H28" s="74" t="n">
         <v>1</v>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="J28" s="75" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="K28" s="74" t="n">
         <v>2</v>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M28" s="75" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="6" t="n"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M29" s="75" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="N29" s="13" t="n"/>
       <c r="O29" s="6" t="n"/>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="G30" s="75" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="H30" s="74" t="n">
         <v>2</v>
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="J30" s="75" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="74" t="n">
         <v>2</v>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="M30" s="75" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="6" t="n"/>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="G31" s="75" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="H31" s="74" t="n">
         <v>2</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="J31" s="75" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="K31" s="74" t="n">
         <v>1</v>
@@ -6357,7 +6357,7 @@
       <c r="C33" s="65" t="n"/>
       <c r="D33" s="60" t="n"/>
       <c r="E33" s="78" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F33" s="63" t="n"/>
       <c r="G33" s="36" t="inlineStr">
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="H33" s="78" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I33" s="63" t="n"/>
       <c r="J33" s="36" t="inlineStr">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="K33" s="78" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="L33" s="63" t="n"/>
       <c r="M33" s="36" t="inlineStr">
@@ -6959,7 +6959,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>產生日期：2026-09-12　產生器：engine/export_xlsx.py</t>
+          <t>產生日期：2026-09-13　產生器：engine/export_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = -6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -10287,7 +10287,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = -15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -10409,7 +10409,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10531,7 +10531,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-11.25</v>
+        <v>11.25</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = -1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = -1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -12649,7 +12649,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -16111,7 +16111,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -16233,7 +16233,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = +2.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -17251,7 +17251,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -17455,7 +17455,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -17577,7 +17577,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>-21</v>
+        <v>21</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>-14.75</v>
+        <v>14.75</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>-16.75</v>
+        <v>16.75</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>

--- a/output/log/fourthVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/log/fourthVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1167,7 +1167,7 @@
         <t>【AI判定】容積率（P002-00 修正百分比）
 填寫值：6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1491,7 +1491,7 @@
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
 填寫值：15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1518,7 +1518,7 @@
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1545,7 +1545,7 @@
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1590,7 +1590,7 @@
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1617,7 +1617,7 @@
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1644,7 +1644,7 @@
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1689,7 +1689,7 @@
         <t>【AI判定】接近大型車站之程度（P002-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.near_station</t>
       </text>
     </comment>
@@ -1842,7 +1842,7 @@
         <t>【AI判定】站牌之接近程度或密集程度（P004-00 修正百分比）
 填寫值：1.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(2−1)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_busstop</t>
       </text>
     </comment>
@@ -1941,7 +1941,7 @@
         <t>【AI判定】交流道之有無及接近交流道之程度（P004-00 修正百分比）
 填寫值：1.0
 資料來源：比準地 P001-00 稍劣(4) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(5−4)×1.0 = +1.00
 基準表項目ID：shulin.regional.near_interchange</t>
       </text>
     </comment>
@@ -1986,7 +1986,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
 填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2013,7 +2013,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2040,7 +2040,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2859,7 +2859,7 @@
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P002-00 修正百分比）
 填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2886,7 +2886,7 @@
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P003-00 修正百分比）
 填寫值：-4.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2913,7 +2913,7 @@
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P004-00 修正百分比）
 填寫值：-2.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(2−3)×2.0 = -2.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3012,7 +3012,7 @@
         <t>【AI判定】接近公園（里鄰公園、一般公園）、廣場、徒步區之程度（P004-00 修正百分比）
 填寫值：4.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 普通(3)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
 基準表項目ID：shulin.regional.near_park</t>
       </text>
     </comment>
@@ -3057,7 +3057,7 @@
         <t>【AI判定】接近觀光遊憩設施之程度（P002-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3084,7 +3084,7 @@
         <t>【AI判定】接近觀光遊憩設施之程度（P003-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3111,7 +3111,7 @@
         <t>【AI判定】接近觀光遊憩設施之程度（P004-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3156,7 +3156,7 @@
         <t>【AI判定】停車場地之便利程度（P002-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3183,7 +3183,7 @@
         <t>【AI判定】停車場地之便利程度（P003-00 修正百分比）
 填寫值：1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = +1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(2−1)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = +1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(5−4)×1.0 = +1.00</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = -2.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(2−3)×2.0 = -2.00</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
